--- a/Starfront/文档/配置表/BattleStartResource.xlsx
+++ b/Starfront/文档/配置表/BattleStartResource.xlsx
@@ -1347,174 +1347,283 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
-  <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="8.625" customWidth="1"/>
-    <col min="3" max="3" width="19" customWidth="1"/>
-    <col min="4" max="4" width="11.5" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="7.75" customWidth="1"/>
-    <col min="7" max="7" width="15.625" customWidth="1"/>
-    <col min="8" max="8" width="13.75" customWidth="1"/>
-    <col min="9" max="9" width="10.625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="17.25" spans="1:9">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" ht="17.25" spans="1:9">
-      <c r="A2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" ht="17.25" spans="1:9">
-      <c r="A3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" ht="17.25" spans="1:9">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5">
-        <v>1001</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="5">
-        <v>1001</v>
-      </c>
-      <c r="F4" s="5">
-        <v>1001</v>
-      </c>
-      <c r="G4" s="5">
-        <v>50</v>
-      </c>
-      <c r="H4" s="5">
-        <v>100</v>
-      </c>
-      <c r="I4" s="5">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" ht="17.25" spans="1:9">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5">
-        <v>1001</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="5">
-        <v>1001</v>
-      </c>
-      <c r="F5" s="5">
-        <v>1001</v>
-      </c>
-      <c r="G5" s="5">
-        <v>50</v>
-      </c>
-      <c r="H5" s="5">
-        <v>100</v>
-      </c>
-      <c r="I5" s="5">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" sqref="C4:C10000">
-      <formula1>"己方,敌方,绝对中立"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="D4:D10000">
-      <formula1>"远征殖民军,吞星虫族,辉晶族,自治智械"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
+<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <ns0:sheetPr/>
+  <ns0:dimension ref="A1:K7"/>
+  <ns0:sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
+  <ns0:cols>
+    <ns0:col min="1" max="1" width="8" customWidth="1"/>
+    <ns0:col min="2" max="2" width="8.625" customWidth="1"/>
+    <ns0:col min="3" max="3" width="19" customWidth="1"/>
+    <ns0:col min="4" max="4" width="11.5" customWidth="1"/>
+    <ns0:col min="5" max="5" width="16" customWidth="1"/>
+    <ns0:col min="6" max="6" width="7.75" customWidth="1"/>
+    <ns0:col min="7" max="7" width="15.625" customWidth="1"/>
+    <ns0:col min="8" max="8" width="13.75" customWidth="1"/>
+    <ns0:col min="9" max="9" width="10.625" customWidth="1"/>
+    <ns0:col min="10" max="10" width="28" customWidth="1"/>
+    <ns0:col min="11" max="11" width="30" customWidth="1"/>
+  </ns0:cols>
+  <ns0:sheetData>
+    <ns0:row r="1" ht="17.25" spans="1:9">
+      <ns0:c r="A1" s="1" t="s">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+      <ns0:c r="B1" s="2" t="s">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="C1" s="2" t="s">
+        <ns0:v>2</ns0:v>
+      </ns0:c>
+      <ns0:c r="D1" s="2" t="s">
+        <ns0:v>3</ns0:v>
+      </ns0:c>
+      <ns0:c r="E1" s="2" t="s">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
+      <ns0:c r="F1" s="2" t="s">
+        <ns0:v>5</ns0:v>
+      </ns0:c>
+      <ns0:c r="G1" s="2" t="s">
+        <ns0:v>6</ns0:v>
+      </ns0:c>
+      <ns0:c r="H1" s="2" t="s">
+        <ns0:v>7</ns0:v>
+      </ns0:c>
+      <ns0:c r="I1" s="2" t="s">
+        <ns0:v>8</ns0:v>
+      </ns0:c>
+      <ns0:c r="J1" t="str" s="2">
+        <ns0:v>controlType</ns0:v>
+      </ns0:c>
+      <ns0:c r="K1" t="str" s="2">
+        <ns0:v>aiProfileId</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="2" ht="17.25" spans="1:9">
+      <ns0:c r="A2" s="3" t="s">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="B2" s="4" t="s">
+        <ns0:v>10</ns0:v>
+      </ns0:c>
+      <ns0:c r="C2" s="4" t="s">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="D2" s="4" t="s">
+        <ns0:v>12</ns0:v>
+      </ns0:c>
+      <ns0:c r="E2" s="4" t="s">
+        <ns0:v>13</ns0:v>
+      </ns0:c>
+      <ns0:c r="F2" s="4" t="s">
+        <ns0:v>14</ns0:v>
+      </ns0:c>
+      <ns0:c r="G2" s="4" t="s">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="H2" s="4" t="s">
+        <ns0:v>16</ns0:v>
+      </ns0:c>
+      <ns0:c r="I2" s="4" t="s">
+        <ns0:v>17</ns0:v>
+      </ns0:c>
+      <ns0:c r="J2" t="str" s="4">
+        <ns0:v>玩家控制类型</ns0:v>
+      </ns0:c>
+      <ns0:c r="K2" t="str" s="4">
+        <ns0:v>电脑策略ID（真人填0）</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="3" ht="17.25" spans="1:9">
+      <ns0:c r="A3" s="1" t="s">
+        <ns0:v>18</ns0:v>
+      </ns0:c>
+      <ns0:c r="B3" s="2" t="s">
+        <ns0:v>19</ns0:v>
+      </ns0:c>
+      <ns0:c r="C3" s="2" t="s">
+        <ns0:v>20</ns0:v>
+      </ns0:c>
+      <ns0:c r="D3" s="2" t="s">
+        <ns0:v>21</ns0:v>
+      </ns0:c>
+      <ns0:c r="E3" s="2" t="s">
+        <ns0:v>19</ns0:v>
+      </ns0:c>
+      <ns0:c r="F3" s="2" t="s">
+        <ns0:v>19</ns0:v>
+      </ns0:c>
+      <ns0:c r="G3" s="2" t="s">
+        <ns0:v>19</ns0:v>
+      </ns0:c>
+      <ns0:c r="H3" s="2" t="s">
+        <ns0:v>19</ns0:v>
+      </ns0:c>
+      <ns0:c r="I3" s="2" t="s">
+        <ns0:v>19</ns0:v>
+      </ns0:c>
+      <ns0:c r="J3" t="str" s="2">
+        <ns0:v>BattlePlayerControlType</ns0:v>
+      </ns0:c>
+      <ns0:c r="K3" t="str" s="2">
+        <ns0:v>int</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="4" ht="17.25" spans="1:9">
+      <ns0:c r="A4" s="5"/>
+      <ns0:c r="B4" s="5">
+        <ns0:v>1001</ns0:v>
+      </ns0:c>
+      <ns0:c r="C4" s="5" t="s">
+        <ns0:v>22</ns0:v>
+      </ns0:c>
+      <ns0:c r="D4" s="5" t="s">
+        <ns0:v>23</ns0:v>
+      </ns0:c>
+      <ns0:c r="E4" s="5">
+        <ns0:v>1001</ns0:v>
+      </ns0:c>
+      <ns0:c r="F4" s="5">
+        <ns0:v>1001</ns0:v>
+      </ns0:c>
+      <ns0:c r="G4" s="5">
+        <ns0:v>50</ns0:v>
+      </ns0:c>
+      <ns0:c r="H4" s="5">
+        <ns0:v>100</ns0:v>
+      </ns0:c>
+      <ns0:c r="I4" s="5">
+        <ns0:v>8</ns0:v>
+      </ns0:c>
+      <ns0:c r="J4" t="str" s="5">
+        <ns0:v>真人</ns0:v>
+      </ns0:c>
+      <ns0:c r="K4" t="n" s="5">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="5" ht="17.25" spans="1:9">
+      <ns0:c r="A5" s="5"/>
+      <ns0:c r="B5" s="5">
+        <ns0:v>1001</ns0:v>
+      </ns0:c>
+      <ns0:c r="C5" s="5" t="s">
+        <ns0:v>24</ns0:v>
+      </ns0:c>
+      <ns0:c r="D5" s="5" t="s">
+        <ns0:v>23</ns0:v>
+      </ns0:c>
+      <ns0:c r="E5" s="5">
+        <ns0:v>1001</ns0:v>
+      </ns0:c>
+      <ns0:c r="F5" s="5">
+        <ns0:v>1001</ns0:v>
+      </ns0:c>
+      <ns0:c r="G5" s="5">
+        <ns0:v>50</ns0:v>
+      </ns0:c>
+      <ns0:c r="H5" s="5">
+        <ns0:v>100</ns0:v>
+      </ns0:c>
+      <ns0:c r="I5" s="5">
+        <ns0:v>8</ns0:v>
+      </ns0:c>
+      <ns0:c r="J5" t="str" s="5">
+        <ns0:v>电脑</ns0:v>
+      </ns0:c>
+      <ns0:c r="K5" t="n" s="5">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="6" ht="17.25" spans="1:9">
+      <ns0:c r="A6" s="5"/>
+      <ns0:c r="B6" s="5">
+        <ns0:v>1002</ns0:v>
+      </ns0:c>
+      <ns0:c r="C6" s="5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>己方</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D6" s="5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>远征殖民军</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E6" s="5">
+        <ns0:v>1001</ns0:v>
+      </ns0:c>
+      <ns0:c r="F6" s="5">
+        <ns0:v>1001</ns0:v>
+      </ns0:c>
+      <ns0:c r="G6" s="5">
+        <ns0:v>50</ns0:v>
+      </ns0:c>
+      <ns0:c r="H6" s="5">
+        <ns0:v>100</ns0:v>
+      </ns0:c>
+      <ns0:c r="I6" s="5">
+        <ns0:v>8</ns0:v>
+      </ns0:c>
+      <ns0:c r="J6" t="str" s="5">
+        <ns0:v>真人</ns0:v>
+      </ns0:c>
+      <ns0:c r="K6" t="n" s="5">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="7" ht="17.25" spans="1:9">
+      <ns0:c r="A7" s="5"/>
+      <ns0:c r="B7" s="5">
+        <ns0:v>1002</ns0:v>
+      </ns0:c>
+      <ns0:c r="C7" s="5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>敌方</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D7" s="5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>远征殖民军</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E7" s="5">
+        <ns0:v>1001</ns0:v>
+      </ns0:c>
+      <ns0:c r="F7" s="5">
+        <ns0:v>1001</ns0:v>
+      </ns0:c>
+      <ns0:c r="G7" s="5">
+        <ns0:v>50</ns0:v>
+      </ns0:c>
+      <ns0:c r="H7" s="5">
+        <ns0:v>100</ns0:v>
+      </ns0:c>
+      <ns0:c r="I7" s="5">
+        <ns0:v>8</ns0:v>
+      </ns0:c>
+      <ns0:c r="J7" t="str" s="5">
+        <ns0:v>电脑</ns0:v>
+      </ns0:c>
+      <ns0:c r="K7" t="n" s="5">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+    </ns0:row>
+  </ns0:sheetData>
+  <ns0:dataValidations count="3">
+    <ns0:dataValidation type="list" sqref="C4:C10000">
+      <ns0:formula1>"己方,敌方,绝对中立"</ns0:formula1>
+    </ns0:dataValidation>
+    <ns0:dataValidation type="list" sqref="D4:D10000">
+      <ns0:formula1>"远征殖民军,吞星虫族,辉晶族,自治智械"</ns0:formula1>
+    </ns0:dataValidation>
+    <ns0:dataValidation type="list" sqref="J4:J10000" showErrorMessage="1" errorStyle="stop">
+      <ns0:formula1>"真人,电脑"</ns0:formula1>
+    </ns0:dataValidation>
+  </ns0:dataValidations>
+  <ns0:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ns0:headerFooter/>
+  <ns0:legacyDrawing ns1:id="rId2"/>
+</ns0:worksheet>
 </file>